--- a/files/九龙-茶果岭、油塘及鲤鱼门-朗誉.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-朗誉.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -29813,4 +30010,5848 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$589万
+$22,582/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$694万
+$20,976/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$721万
+$21,382/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$720万
+$21,103/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$784万
+$21,534/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$706万
+$21,928/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$681万
+$22,313/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$586万
+$22,448/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$690万
+$20,850/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$716万
+$21,255/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$715万
+$20,977/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$779万
+$21,405/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$702万
+$21,798/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$676万
+$22,179/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$978万
+$20,636/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$568万
+$21,761/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$674万
+$20,369/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$933万
+$18,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$700万
+$20,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$699万
+$20,492/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$912万
+$19,566/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$761万
+$20,911/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$686万
+$21,294/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$661万
+$21,667/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$937万
+$17,951/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$976万
+$20,595/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$567万
+$21,730/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$672万
+$20,308/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$698万
+$20,702/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$697万
+$20,430/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$910万
+$19,527/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$759万
+$20,848/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$684万
+$21,230/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$659万
+$21,602/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$1099万
+$21,056/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$972万
+$20,513/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$407万
+$15,594/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$671万
+$20,267/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$696万
+$20,661/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$695万
+$20,390/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$906万
+$19,449/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$757万
+$20,807/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$682万
+$21,188/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$658万
+$21,559/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$1093万
+$20,930/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$970万
+$20,472/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$407万
+$15,579/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$670万
+$20,247/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$696万
+$20,640/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$695万
+$20,369/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$905万
+$19,410/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$757万
+$20,786/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$682万
+$21,166/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$657万
+$21,538/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$1089万
+$20,867/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$745万
+$15,713/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$406万
+$15,562/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$499万
+$15,079/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$804万
+$15,765/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$518万
+$15,371/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$517万
+$15,170/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$694万
+$14,898/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$563万
+$15,479/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$508万
+$15,763/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$489万
+$16,040/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$890万
+$17,041/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$743万
+$15,681/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$493万
+$18,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$499万
+$15,063/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$802万
+$15,718/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$517万
+$15,356/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$517万
+$15,155/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$693万
+$14,868/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$563万
+$15,464/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$507万
+$15,748/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$489万
+$16,024/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$837万
+$16,028/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$742万
+$15,650/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$490万
+$18,785/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$498万
+$15,048/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$791万
+$15,516/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$517万
+$15,340/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$516万
+$15,139/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$901万
+$19,343/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$562万
+$15,449/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$507万
+$15,732/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$488万
+$16,008/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$834万
+$15,980/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$740万
+$15,619/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$487万
+$18,673/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$498万
+$15,033/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$789万
+$15,470/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$516万
+$15,325/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$516万
+$15,124/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$690万
+$14,809/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$562万
+$15,433/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$506万
+$15,716/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$668万
+$21,889/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$832万
+$15,933/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$739万
+$15,588/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$490万
+$18,780/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+$497万
+$15,064/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$787万
+$15,423/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$516万
+$15,310/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$515万
+$15,109/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$689万
+$14,779/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$561万
+$15,418/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$506万
+$15,700/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$487万
+$15,976/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$829万
+$15,885/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$737万
+$15,557/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$482万
+$18,451/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$497万
+$15,003/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$1025万
+$20,104/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$515万
+$15,294/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$515万
+$15,094/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$885万
+$18,999/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$561万
+$15,403/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$505万
+$15,684/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$487万
+$15,959/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$827万
+$15,837/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$736万
+$15,526/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$479万
+$18,341/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$496万
+$14,988/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$1019万
+$19,984/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$515万
+$15,279/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$514万
+$15,079/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$880万
+$18,886/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$560万
+$15,387/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$505万
+$15,669/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$486万
+$15,944/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$824万
+$15,790/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$733万
+$15,464/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$479万
+$18,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$645万
+$19,484/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$1007万
+$19,747/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$514万
+$15,249/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$513万
+$15,049/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$870万
+$18,662/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$559万
+$15,356/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$504万
+$15,638/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$485万
+$15,912/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$819万
+$15,696/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$975万
+$20,565/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$470万
+$18,015/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$649万
+$19,596/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$1001万
+$19,629/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$513万
+$15,234/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$513万
+$15,034/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$864万
+$18,551/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$558万
+$15,341/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$665万
+$20,653/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$485万
+$15,896/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$817万
+$15,649/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$730万
+$15,402/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$467万
+$17,908/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$637万
+$19,252/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$819万
+$16,058/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$513万
+$15,218/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$512万
+$15,019/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$859万
+$18,440/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$558万
+$15,326/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$503万
+$15,606/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$484万
+$15,880/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$814万
+$15,602/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$729万
+$15,372/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$465万
+$17,801/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$641万
+$19,363/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$1001万
+$19,624/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$512万
+$15,203/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$512万
+$15,004/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$700万
+$15,012/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$557万
+$15,310/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$502万
+$15,591/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$636万
+$20,867/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$812万
+$15,555/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$947万
+$19,969/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$462万
+$17,695/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$630万
+$19,023/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$964万
+$18,902/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$512万
+$15,188/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$511万
+$14,989/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$849万
+$18,221/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$557万
+$15,295/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$502万
+$15,575/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$633万
+$20,742/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$1006万
+$19,279/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$906万
+$19,123/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$459万
+$17,589/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$626万
+$18,910/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$958万
+$18,789/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$511万
+$15,172/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$511万
+$14,974/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$844万
+$18,112/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$556万
+$15,280/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$501万
+$15,560/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$629万
+$20,619/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$1000万
+$19,164/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$901万
+$19,009/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$456万
+$17,484/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$622万
+$18,797/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$953万
+$18,677/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$669万
+$19,838/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$510万
+$14,959/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$839万
+$18,004/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$556万
+$15,265/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$501万
+$15,544/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$617万
+$20,231/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$986万
+$18,896/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$896万
+$18,895/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$470万
+$17,993/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$506万
+$15,300/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$947万
+$18,566/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$642万
+$19,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$510万
+$14,944/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$834万
+$17,897/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$555万
+$15,249/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$500万
+$15,529/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$613万
+$20,110/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$980万
+$18,783/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$890万
+$18,783/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$419万
+$16,066/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$615万
+$18,574/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$941万
+$18,455/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$638万
+$18,934/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$509万
+$14,914/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$839万
+$17,999/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$554万
+$15,219/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$638万
+$19,806/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$603万
+$19,758/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$963万
+$18,454/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$880万
+$18,560/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$399万
+$15,285/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$615万
+$18,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$930万
+$18,236/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$638万
+$18,930/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$508万
+$14,899/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$829万
+$17,786/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$553万
+$15,204/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$649万
+$20,146/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$495万
+$16,227/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$952万
+$18,235/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$717万
+$15,128/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$459万
+$17,569/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$611万
+$18,458/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$924万
+$18,127/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$627万
+$18,598/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$645万
+$18,922/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$824万
+$17,680/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$695万
+$19,084/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$626万
+$19,454/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$592万
+$19,407/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$957万
+$18,339/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$880万
+$18,555/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$440万
+$16,869/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$607万
+$18,348/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$919万
+$18,019/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$623万
+$18,487/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$634万
+$18,591/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$809万
+$17,370/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$552万
+$15,173/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$623万
+$19,338/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$595万
+$19,518/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$941万
+$18,018/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$864万
+$18,230/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$453万
+$17,360/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$604万
+$18,239/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$914万
+$17,912/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$619万
+$18,377/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$630万
+$18,479/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$805万
+$17,266/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$552万
+$15,158/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$626万
+$19,449/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$592万
+$19,402/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$935万
+$17,911/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$734万
+$15,489/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$435万
+$16,668/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$593万
+$17,919/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$908万
+$17,805/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$623万
+$18,482/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$626万
+$18,370/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$800万
+$17,164/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$682万
+$18,745/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$615万
+$19,108/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$588万
+$19,286/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$929万
+$17,804/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$854万
+$18,013/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$432万
+$16,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$590万
+$17,812/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$913万
+$17,907/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$619万
+$18,372/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$630万
+$18,474/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$663万
+$14,229/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$678万
+$18,633/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$612万
+$18,994/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$578万
+$18,948/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$935万
+$17,906/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$849万
+$17,905/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$430万
+$16,470/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$586万
+$17,706/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$897万
+$17,593/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$615万
+$18,262/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$619万
+$18,151/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$800万
+$17,159/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$674万
+$18,522/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$615万
+$19,103/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$574万
+$18,835/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$918万
+$17,592/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$844万
+$17,799/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 260呎 (开放式)
+$432万
+$16,628/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$583万
+$17,601/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$892万
+$17,488/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$612万
+$18,153/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$615万
+$18,043/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$786万
+$16,858/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$670万
+$18,411/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$604万
+$18,768/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$571万
+$18,723/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$913万
+$17,487/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$843万
+$17,795/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$422万
+$16,177/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+$576万
+$17,445/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$892万
+$17,484/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$597万
+$17,729/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$626万
+$18,353/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$776万
+$16,658/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$662万
+$18,193/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$611万
+$18,982/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$564万
+$18,501/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L35" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$902万
+$17,280/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>A | 474呎 (2房)
+$817万
+$17,243/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>B | 261呎 (开放式)
+$429万
+$16,420/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>C | 331呎 (1房)
+$477万
+$14,402/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>D | 510呎 (2房)
+$864万
+$16,942/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$586万
+$17,382/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>F | 341呎 (1房)
+$596万
+$17,479/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>G | 466呎 (2房)
+$761万
+$16,332/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>H | 364呎 (1房)
+$649万
+$17,836/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>J | 322呎 (1房)
+$585万
+$18,182/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$481万
+$15,780/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L36" s="23" t="inlineStr">
+        <is>
+          <t>L | 522呎 (2房)
+$884万
+$16,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1601呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 970呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr"/>
+      <c r="F5" s="24" t="inlineStr"/>
+      <c r="G5" s="24" t="inlineStr"/>
+      <c r="H5" s="24" t="inlineStr"/>
+      <c r="I5" s="24" t="inlineStr"/>
+      <c r="J5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$918万
+$19,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$724万
+$23,200/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$778万
+$23,496/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$578万
+$23,493/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$778万
+$23,006/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$908万
+$19,492/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1359万
+$23,504/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$720万
+$23,062/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$773万
+$23,356/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$574万
+$23,352/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1337万
+$22,694/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$773万
+$22,869/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$910万
+$18,273/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1326万
+$22,943/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$702万
+$22,512/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$755万
+$22,799/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$561万
+$22,795/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$755万
+$22,323/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$956万
+$19,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$821万
+$17,620/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$992万
+$17,167/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$530万
+$17,054/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$572万
+$17,292/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 245呎 (开放式)
+$423万
+$17,259/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1289万
+$21,885/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$565万
+$16,730/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$907万
+$18,209/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 731呎 (3房)
+$1380万
+$18,874/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$873万
+$18,740/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1027万
+$17,765/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$559万
+$17,983/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$743万
+$22,455/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$552万
+$22,452/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1285万
+$21,819/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$596万
+$17,633/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$847万
+$17,004/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1323万
+$18,122/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$847万
+$18,173/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$986万
+$17,065/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$529万
+$17,020/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+$603万
+$18,161/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 245呎 (开放式)
+$453万
+$18,477/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1281万
+$21,754/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$564万
+$16,696/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$844万
+$16,954/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1438万
+$19,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$814万
+$17,463/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$932万
+$16,124/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$490万
+$15,690/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+$571万
+$17,188/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>F | 245呎 (开放式)
+$422万
+$17,207/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$1018万
+$17,247/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$522万
+$15,453/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$788万
+$15,816/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1431万
+$19,600/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$762万
+$16,345/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$929万
+$16,075/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$489万
+$15,674/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$528万
+$15,944/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$383万
+$15,561/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1274万
+$21,624/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$522万
+$15,437/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$785万
+$15,769/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1237万
+$16,942/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$759万
+$16,296/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$926万
+$16,027/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$489万
+$15,659/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$527万
+$15,928/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$382万
+$15,545/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$987万
+$16,734/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$521万
+$15,422/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$768万
+$15,413/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1233万
+$16,892/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$757万
+$16,247/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$924万
+$15,979/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$488万
+$15,643/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$527万
+$15,912/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$382万
+$15,529/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$1008万
+$17,092/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$521万
+$15,407/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$765万
+$15,367/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1554万
+$21,287/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$973万
+$20,872/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$921万
+$15,931/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$488万
+$15,627/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$526万
+$15,896/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$382万
+$15,514/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$1005万
+$17,041/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$536万
+$15,848/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$763万
+$15,321/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1563万
+$21,409/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$995万
+$21,358/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1161万
+$20,088/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$487万
+$15,612/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$526万
+$15,880/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$381万
+$15,498/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$950万
+$16,101/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$535万
+$15,832/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$761万
+$15,275/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1218万
+$16,690/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$748万
+$16,054/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1147万
+$19,850/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$652万
+$20,883/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$525万
+$15,849/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$381万
+$15,468/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$973万
+$16,485/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$534万
+$15,801/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$756万
+$15,184/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1517万
+$20,785/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$950万
+$20,380/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1154万
+$19,964/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$486万
+$15,565/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$524万
+$15,833/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$515万
+$20,932/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$970万
+$16,436/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$534万
+$15,785/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$754万
+$15,139/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1247万
+$17,088/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$944万
+$20,258/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$907万
+$15,695/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$635万
+$20,368/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$524万
+$15,817/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$380万
+$15,436/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$967万
+$16,415/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$533万
+$15,769/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$752万
+$15,093/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1244万
+$17,037/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$938万
+$20,137/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1140万
+$19,726/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$624万
+$20,011/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$523万
+$15,801/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$379万
+$15,421/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$964万
+$16,366/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$532万
+$15,753/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$749万
+$15,048/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1240万
+$16,987/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$739万
+$15,862/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$902万
+$15,601/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$621万
+$19,892/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$522万
+$15,785/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$379万
+$15,406/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$985万
+$16,688/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$558万
+$16,497/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$747万
+$15,003/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1481万
+$20,293/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$737万
+$15,815/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1114万
+$19,265/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$624万
+$20,005/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$522万
+$15,770/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$379万
+$15,390/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$982万
+$16,666/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$531万
+$15,722/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$955万
+$19,169/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1473万
+$20,172/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$933万
+$20,012/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1107万
+$19,150/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$620万
+$19,886/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$695万
+$20,993/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 245呎 (开放式)
+$378万
+$15,438/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$955万
+$16,220/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$516万
+$15,253/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$949万
+$19,055/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 731呎 (3房)
+$1402万
+$19,174/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$916万
+$19,661/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1100万
+$19,036/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$610万
+$19,538/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$521万
+$15,738/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$378万
+$15,360/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$925万
+$15,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$515万
+$15,238/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$943万
+$18,941/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1455万
+$19,932/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$893万
+$19,161/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1085万
+$18,770/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$613万
+$19,713/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$687万
+$20,744/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$480万
+$19,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1137万
+$19,302/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$514万
+$15,208/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$938万
+$18,829/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$882万
+$18,933/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1060万
+$18,331/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$606万
+$19,417/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$519万
+$15,691/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$477万
+$19,404/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1156万
+$19,633/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$514万
+$15,193/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$927万
+$18,605/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1214万
+$16,634/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$887万
+$19,042/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1066万
+$18,437/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$602万
+$19,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$519万
+$15,675/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$482万
+$19,574/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$914万
+$15,513/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$584万
+$17,284/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$921万
+$18,494/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1211万
+$16,585/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$872万
+$18,708/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1047万
+$18,113/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$480万
+$15,395/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$651万
+$19,675/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$474万
+$19,289/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$911万
+$15,466/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$528万
+$15,612/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$916万
+$18,384/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1207万
+$16,535/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$867万
+$18,597/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1053万
+$18,217/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$588万
+$18,850/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$518万
+$15,644/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$479万
+$19,457/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$908万
+$15,420/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$553万
+$16,350/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$910万
+$18,274/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1203万
+$16,485/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$872万
+$18,703/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1035万
+$17,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$605万
+$19,398/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$517万
+$15,629/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$472万
+$19,174/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$933万
+$15,835/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$527万
+$15,582/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$905万
+$18,165/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 731呎 (3房)
+$1200万
+$16,414/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$856万
+$18,375/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1028万
+$17,791/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$479万
+$15,349/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$517万
+$15,613/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>F | 245呎 (开放式)
+$476万
+$19,420/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$939万
+$15,947/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$511万
+$15,117/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$910万
+$18,269/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$851万
+$18,266/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1022万
+$17,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$478万
+$15,333/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$516万
+$15,597/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$474万
+$19,283/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1084万
+$18,400/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$510万
+$15,102/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$894万
+$17,949/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1339万
+$18,338/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$846万
+$18,157/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1028万
+$17,787/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$574万
+$18,404/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$632万
+$19,095/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$459万
+$18,644/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>G | 589呎 (2房)
+$1185万
+$20,124/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$509万
+$15,072/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$889万
+$17,842/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+$1323万
+$18,121/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$836万
+$17,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$1004万
+$17,371/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$567万
+$18,186/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$643万
+$19,424/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$448万
+$18,209/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$970万
+$16,445/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$504万
+$14,922/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$878万
+$17,631/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>A | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$820万
+$17,590/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>C | 578呎 (2房)
+$984万
+$17,031/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>D | 312呎 (1房)
+$576万
+$18,458/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$612万
+$18,499/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$439万
+$17,852/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>G | 590呎 (2房)
+$926万
+$15,687/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>H | 338呎 (1房)
+$499万
+$14,775/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>J | 498呎 (2房)
+$861万
+$17,285/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-朗誉.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-朗誉.xlsx
@@ -671,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
